--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E97578D-DC5B-4D5A-8986-C9E3C63B3405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7BFE75-CCFB-4264-B809-2FDCBA7F8B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>▢ SLAM</t>
   </si>
   <si>
-    <t xml:space="preserve">Adresse URL du portfolio : </t>
-  </si>
-  <si>
     <t>Compétences mises en œuvre
 Réalisations professionnelles
 (intitulé et liste des documents et productions associés)</t>
@@ -301,6 +298,9 @@
   </si>
   <si>
     <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://hugo-lemarchand.github.io/portfolio/</t>
   </si>
 </sst>
 </file>
@@ -966,15 +966,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1006,30 +1030,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1351,56 +1351,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="53" t="s">
+      <c r="A3" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="54"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="41"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1412,63 +1412,63 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="B6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="43"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="H7" s="19" t="s">
         <v>20</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>21</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1507,16 +1507,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="A8" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1555,21 +1555,21 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="28"/>
       <c r="G9" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9"/>
@@ -1610,23 +1610,23 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10"/>
@@ -1667,23 +1667,23 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11"/>
@@ -1724,22 +1724,22 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="28"/>
       <c r="G12" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -2048,16 +2048,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="A19" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2096,19 +2096,19 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="28"/>
       <c r="G20" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20"/>
@@ -2149,19 +2149,19 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="28"/>
       <c r="I21"/>
@@ -2202,21 +2202,21 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" s="28"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22"/>
@@ -2257,16 +2257,16 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="30" t="s">
         <v>29</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>30</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -2452,16 +2452,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="A27" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2500,19 +2500,19 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="27"/>
       <c r="D28" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H28" s="28"/>
       <c r="I28"/>
@@ -2553,19 +2553,19 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="28"/>
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29"/>
@@ -2606,21 +2606,21 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" s="28"/>
       <c r="F30" s="28"/>
       <c r="G30" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" s="28"/>
       <c r="I30"/>
@@ -2661,16 +2661,16 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>29</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>30</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
       <c r="F31" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="F32" s="28"/>
       <c r="G32" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -2948,11 +2948,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2960,6 +2955,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2970,27 +2970,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3191,26 +3170,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3227,4 +3208,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7BFE75-CCFB-4264-B809-2FDCBA7F8B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D75515-EA91-4853-880F-37F8DBE6A4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -966,9 +966,48 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -991,45 +1030,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1351,56 +1351,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="40" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="41"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="54"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1412,22 +1412,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1450,8 +1450,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="43"/>
-      <c r="B7" s="51"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
@@ -1507,16 +1507,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -2048,16 +2048,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2452,16 +2452,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2711,24 +2711,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="A32" s="26"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="28"/>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="F32" s="28"/>
-      <c r="G32" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2948,6 +2938,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2955,11 +2950,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2970,6 +2960,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3170,28 +3181,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3208,23 +3217,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D75515-EA91-4853-880F-37F8DBE6A4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4458DD-2997-42A0-9B4C-7F48E6BAA37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -206,25 +206,6 @@
   </si>
   <si>
     <t>01/09/2024 au 01/09/2026</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Installation serveur Windows Server</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : (AD, DNS, DHCP, VPN)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -301,6 +282,38 @@
   </si>
   <si>
     <t>Adresse URL du portfolio : https://hugo-lemarchand.github.io/portfolio/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Installation serveur Windows Server</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> : (AD, DNS, DHCP)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Installation et configuration d'un serveur de virtualisation Proxmox VE : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AD, GLPI, Zabbix, Wazuh, Server Backup)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -966,15 +979,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1006,30 +1043,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1351,56 +1364,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="53" t="s">
+      <c r="A3" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="54"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="41"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1412,22 +1425,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="A5" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="50" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1450,8 +1463,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="51"/>
       <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
@@ -1507,16 +1520,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1555,7 +1568,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>29</v>
@@ -1610,7 +1623,7 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>29</v>
@@ -1667,7 +1680,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>29</v>
@@ -1724,9 +1737,11 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="30"/>
+        <v>33</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="C12" s="28" t="s">
         <v>24</v>
       </c>
@@ -1778,14 +1793,22 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+      <c r="G13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -2048,16 +2071,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2308,7 +2331,7 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="30" t="s">
         <v>29</v>
@@ -2452,16 +2475,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2938,11 +2961,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2950,6 +2968,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2960,27 +2983,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3181,26 +3183,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3217,4 +3221,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4458DD-2997-42A0-9B4C-7F48E6BAA37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9940DAB-04A3-4E37-9A11-C01D05659313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -282,25 +282,6 @@
   </si>
   <si>
     <t>Adresse URL du portfolio : https://hugo-lemarchand.github.io/portfolio/</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Installation serveur Windows Server</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : (AD, DNS, DHCP)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1567,7 +1548,7 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="30" t="s">
@@ -1584,7 +1565,9 @@
       <c r="G9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1793,22 +1776,14 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>29</v>
-      </c>
+      <c r="A13" s="26"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
-      <c r="G13" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9940DAB-04A3-4E37-9A11-C01D05659313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02B398-378B-4D4E-BAA1-33C7C90E8413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -294,6 +294,19 @@
         <family val="2"/>
       </rPr>
       <t>(AD, GLPI, Zabbix, Wazuh, Server Backup)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Certification : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cisco </t>
     </r>
   </si>
 </sst>
@@ -1561,13 +1574,13 @@
         <v>24</v>
       </c>
       <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
+      <c r="F9" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="G9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="H9" s="28"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1614,16 +1627,12 @@
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="D10" s="28"/>
       <c r="E10" s="28"/>
       <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="G10" s="28"/>
       <c r="H10" s="28"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -1736,9 +1745,7 @@
       <c r="G12" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="H12" s="28"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1776,14 +1783,20 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+      <c r="H13" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02B398-378B-4D4E-BAA1-33C7C90E8413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE242D36-E592-44E4-9E6A-44CD9B7234DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="42">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -256,28 +256,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Mise à jour des schémas et documentation technique IT : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Confluence</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
@@ -308,6 +286,28 @@
       </rPr>
       <t xml:space="preserve">Cisco </t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Migration Intune : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">migration utilisateurs domaine vers Intune </t>
+    </r>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Zabbix </t>
+  </si>
+  <si>
+    <t>01/12/2025 au 01/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1347,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="182.9296875" style="1" bestFit="1" customWidth="1"/>
@@ -1367,7 +1367,7 @@
       <c r="E1" s="33"/>
       <c r="F1" s="33"/>
       <c r="G1" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H1" s="33"/>
     </row>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>29</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>29</v>
@@ -2318,24 +2318,18 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
-        <v>34</v>
+      <c r="A24" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>24</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2375,12 +2369,12 @@
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="21"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2417,15 +2411,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="14"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A26" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="49"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2462,17 +2458,23 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="28"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2510,16 +2512,16 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="26" t="s">
-        <v>25</v>
+      <c r="A28" s="29" t="s">
+        <v>26</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28" t="s">
+      <c r="C28" s="28" t="s">
         <v>24</v>
       </c>
+      <c r="D28" s="28"/>
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28" t="s">
@@ -2564,7 +2566,7 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="30" t="s">
         <v>29</v>
@@ -2572,7 +2574,9 @@
       <c r="C29" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="28"/>
+      <c r="D29" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28" t="s">
@@ -2617,22 +2621,18 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="G30" s="28"/>
       <c r="H30" s="28"/>
       <c r="I30"/>
       <c r="J30"/>
@@ -2671,18 +2671,16 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="29" t="s">
-        <v>28</v>
+      <c r="A31" s="26" t="s">
+        <v>40</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
-      <c r="F31" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="F31" s="28"/>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31"/>
@@ -2722,14 +2720,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2766,15 +2764,15 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="14"/>
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2811,15 +2809,15 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A34" s="5"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2856,51 +2854,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
@@ -2946,14 +2900,13 @@
     <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE242D36-E592-44E4-9E6A-44CD9B7234DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE13331-A6B6-4F49-8888-465CD1D11A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -241,19 +241,6 @@
   </si>
   <si>
     <t>NOM et prénom : Lemarchand Hugo</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Gestion des comptes sur Active Directory </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: accès</t>
-    </r>
   </si>
   <si>
     <t>SESSION 2026</t>
@@ -1367,7 +1354,7 @@
       <c r="E1" s="33"/>
       <c r="F1" s="33"/>
       <c r="G1" s="33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H1" s="33"/>
     </row>
@@ -1420,7 +1407,7 @@
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
@@ -1562,7 +1549,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>29</v>
@@ -1729,7 +1716,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>29</v>
@@ -1784,7 +1771,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>29</v>
@@ -2319,16 +2306,24 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
+      <c r="C24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="F24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="H24" s="21"/>
       <c r="I24"/>
       <c r="J24"/>
@@ -2672,15 +2667,17 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="F31" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="G31" s="28"/>
       <c r="H31" s="28"/>
       <c r="I31"/>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE13331-A6B6-4F49-8888-465CD1D11A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AB3E71-2556-449E-AC51-710561A877B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="41">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -2211,7 +2211,9 @@
       <c r="D22" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="28"/>
+      <c r="E22" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="F22" s="28"/>
       <c r="G22" s="28" t="s">
         <v>24</v>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AB3E71-2556-449E-AC51-710561A877B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783B8B97-A537-4FC8-B5C2-CB4DEDAA3E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -205,9 +205,6 @@
     </r>
   </si>
   <si>
-    <t>01/09/2024 au 01/09/2026</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Déploiement de services web </t>
     </r>
@@ -296,6 +293,24 @@
   <si>
     <t>01/12/2025 au 01/09/2026</t>
   </si>
+  <si>
+    <t>01/09/2025 au 01/04/2026</t>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/03/2026</t>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/12/2024</t>
+  </si>
+  <si>
+    <t>01/10/2025 au 01/04/2026</t>
+  </si>
+  <si>
+    <t>01/11/2024 au 01/12/2025</t>
+  </si>
+  <si>
+    <t>01/09/2025 au 01/09/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -304,7 +319,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -384,13 +399,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -957,12 +965,48 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -987,44 +1031,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1345,60 +1353,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="40" t="s">
+      <c r="A3" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="41"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="53"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="54" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="17" t="s">
@@ -1406,22 +1414,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="A5" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="41" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1444,8 +1452,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="43"/>
-      <c r="B7" s="51"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
@@ -1501,16 +1509,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1549,10 +1557,10 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>24</v>
@@ -1606,10 +1614,10 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
@@ -1659,10 +1667,10 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>24</v>
@@ -1719,7 +1727,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>24</v>
@@ -1771,10 +1779,10 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
@@ -2046,16 +2054,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2097,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28" t="s">
@@ -2150,7 +2158,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C21" s="28" t="s">
         <v>24</v>
@@ -2203,7 +2211,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C22" s="28" t="s">
         <v>24</v>
@@ -2260,7 +2268,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
@@ -2308,10 +2316,10 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="28" t="s">
         <v>24</v>
@@ -2409,16 +2417,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2460,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C27" s="27"/>
       <c r="D27" s="28" t="s">
@@ -2513,7 +2521,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>24</v>
@@ -2566,7 +2574,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>24</v>
@@ -2621,7 +2629,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -2669,10 +2677,10 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>39</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>40</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -2901,6 +2909,11 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2908,11 +2921,6 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2923,6 +2931,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3123,28 +3152,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3161,23 +3188,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783B8B97-A537-4FC8-B5C2-CB4DEDAA3E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3060ED-3AB1-4D6F-B93A-14A6C15309FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>01/09/2025 au 01/09/2026</t>
+  </si>
+  <si>
+    <t>Veille Technologique</t>
   </si>
 </sst>
 </file>
@@ -1829,14 +1832,20 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>41</v>
+      </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="H14" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -2689,7 +2698,9 @@
         <v>24</v>
       </c>
       <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
+      <c r="H31" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>

--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3060ED-3AB1-4D6F-B93A-14A6C15309FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5799B918-2AD9-4469-B5E1-6F04A7D75E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Tableau de synthèse des réalisations professionnelles</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t xml:space="preserve">Centre de formation: Ensitech </t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>Veille Technologique</t>
+  </si>
+  <si>
+    <t>N° candidat : 02251774686</t>
   </si>
 </sst>
 </file>
@@ -968,15 +968,42 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1009,33 +1036,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1356,124 +1356,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="34"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="53"/>
+      <c r="A3" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="41"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="H4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="17" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="42" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="B6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="43"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="H7" s="19" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1512,16 +1512,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="A8" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1560,23 +1560,23 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9"/>
@@ -1617,18 +1617,18 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="28"/>
       <c r="F10" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
@@ -1670,23 +1670,23 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11" s="28"/>
       <c r="I11"/>
@@ -1727,21 +1727,21 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="28"/>
       <c r="G12" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H12" s="28"/>
       <c r="I12"/>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
@@ -1793,7 +1793,7 @@
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
       <c r="H13" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
@@ -1844,7 +1844,7 @@
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
       <c r="H14" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -2063,16 +2063,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+      <c r="A19" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2111,19 +2111,19 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="28"/>
       <c r="G20" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20"/>
@@ -2164,19 +2164,19 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="28"/>
       <c r="I21"/>
@@ -2217,23 +2217,23 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" s="28"/>
       <c r="G22" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22"/>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
@@ -2325,23 +2325,23 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24"/>
@@ -2426,16 +2426,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A26" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40"/>
+      <c r="A26" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="49"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2474,19 +2474,19 @@
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="27"/>
       <c r="D27" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="28"/>
       <c r="F27" s="28"/>
       <c r="G27" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="28"/>
       <c r="I27"/>
@@ -2527,19 +2527,19 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="28"/>
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28" s="28"/>
       <c r="I28"/>
@@ -2580,21 +2580,21 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29"/>
@@ -2635,16 +2635,16 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
       <c r="F30" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
@@ -2686,20 +2686,20 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>38</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>39</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
       <c r="F31" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" s="28"/>
       <c r="H31" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -2920,11 +2920,6 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2932,6 +2927,11 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2942,27 +2942,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3163,26 +3142,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3199,4 +3180,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5799B918-2AD9-4469-B5E1-6F04A7D75E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466046F0-500C-40A4-AA9C-39883D689715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9090" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -433,73 +433,6 @@
         <color theme="2" tint="-0.749992370372631"/>
       </right>
       <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="thin">
@@ -552,60 +485,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalDown="1">
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </diagonal>
-    </border>
-    <border diagonalDown="1">
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </diagonal>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
     <border>
       <left style="medium">
         <color theme="2" tint="-0.749992370372631"/>
@@ -638,158 +517,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -803,77 +530,29 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
         <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
+      </diagonal>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -890,152 +569,83 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1356,123 +966,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="33"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33" t="s">
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="40" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="41"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="12" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="24" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="27" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="43"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="18" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="28" t="s">
         <v>19</v>
       </c>
       <c r="I7"/>
@@ -1512,16 +1122,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1559,26 +1169,26 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="28"/>
+      <c r="C9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="16"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1616,22 +1226,22 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="C10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1669,26 +1279,26 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="28"/>
+      <c r="C11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="16"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1726,24 +1336,24 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="28"/>
+      <c r="C12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="16"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1781,18 +1391,18 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I13"/>
@@ -1832,18 +1442,18 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I14"/>
@@ -1883,14 +1493,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="25"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1928,14 +1538,14 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1973,14 +1583,14 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -2018,14 +1628,14 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2063,16 +1673,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2110,22 +1720,22 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="28"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2163,22 +1773,22 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="28"/>
+      <c r="C21" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="16"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2216,26 +1826,26 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="28"/>
+      <c r="C22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="16"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2273,20 +1883,20 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2324,26 +1934,26 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="21"/>
+      <c r="C24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="31"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2381,14 +1991,14 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2426,16 +2036,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2473,22 +2083,22 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="28"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="16"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2526,22 +2136,22 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="28"/>
+      <c r="C28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="16"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2579,24 +2189,24 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="28"/>
+      <c r="C29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="16"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2634,20 +2244,20 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2685,20 +2295,20 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I31"/>
@@ -2738,14 +2348,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2783,14 +2393,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="16"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="13"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2920,6 +2530,11 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2927,21 +2542,37 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -3142,28 +2773,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3180,23 +2815,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/E4-Tableau-Synthese.xlsx
+++ b/E4-Tableau-Synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugol\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466046F0-500C-40A4-AA9C-39883D689715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B46A31-770F-4115-BF40-9640EA64582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9090" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -150,56 +150,46 @@
     <t>X</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Gestion des incidents via Jira </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: Prise en charge des tickets utilisateurs, analyse des pannes, résolution des problèmes réseau et logiciels, mise à jour du ticket.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Installation et configuration de postes Windows : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Déploiement de Windows, installation des logiciels, ajout au domaine AD, paramétrage réseau.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Gestion des comptes et groupes Active Directory :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Création de comptes, gestion des groupes, réinitialisation de mots de passe, gestion des GPO.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Gestion d’un projet via Jira (sprints, tâches, workflows, automatisations) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Réalisation de projets : création et organisation des tâches, suivi de l’avancement, collaboration avec l’équipe sur l’outil Jira.</t>
-    </r>
+    <t>NOM et prénom : Lemarchand Hugo</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://hugo-lemarchand.github.io/portfolio/</t>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Zabbix </t>
+  </si>
+  <si>
+    <t>01/12/2025 au 01/09/2026</t>
+  </si>
+  <si>
+    <t>01/09/2025 au 01/04/2026</t>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/03/2026</t>
+  </si>
+  <si>
+    <t>01/09/2024 au 01/12/2024</t>
+  </si>
+  <si>
+    <t>01/10/2025 au 01/04/2026</t>
+  </si>
+  <si>
+    <t>01/11/2024 au 01/12/2025</t>
+  </si>
+  <si>
+    <t>01/09/2025 au 01/09/2026</t>
+  </si>
+  <si>
+    <t>Veille Technologique</t>
+  </si>
+  <si>
+    <t>N° candidat : 02251774686</t>
   </si>
   <si>
     <r>
@@ -207,7 +197,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -216,9 +206,22 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Installation et configuration d'un serveur de virtualisation Proxmox VE : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AD, GLPI, Zabbix, Wazuh, Server Backup)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -226,7 +229,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -234,25 +237,16 @@
     </r>
   </si>
   <si>
-    <t>NOM et prénom : Lemarchand Hugo</t>
-  </si>
-  <si>
-    <t>SESSION 2026</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio : https://hugo-lemarchand.github.io/portfolio/</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Installation et configuration d'un serveur de virtualisation Proxmox VE : </t>
+      <t>Gestion des comptes et groupes Active Directory :</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>(AD, GLPI, Zabbix, Wazuh, Server Backup)</t>
+      <t xml:space="preserve"> Création de comptes, gestion des groupes, réinitialisation de mots de passe, gestion des GPO.</t>
     </r>
   </si>
   <si>
@@ -261,7 +255,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -270,49 +264,55 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Gestion des incidents via Jira </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Prise en charge des tickets utilisateurs, analyse des pannes, résolution des problèmes réseau et logiciels, mise à jour du ticket.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Installation et configuration de postes Windows : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Déploiement de Windows, installation des logiciels, ajout au domaine AD, paramétrage réseau.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gestion d’un projet via Jira (sprints, tâches, workflows, automatisations) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Réalisation de projets : création et organisation des tâches, suivi de l’avancement, collaboration avec l’équipe sur l’outil Jira.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Migration Intune : </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="16"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">migration utilisateurs domaine vers Intune </t>
     </r>
-  </si>
-  <si>
-    <t>01/09/2024 au 01/09/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Zabbix </t>
-  </si>
-  <si>
-    <t>01/12/2025 au 01/09/2026</t>
-  </si>
-  <si>
-    <t>01/09/2025 au 01/04/2026</t>
-  </si>
-  <si>
-    <t>01/09/2024 au 01/03/2026</t>
-  </si>
-  <si>
-    <t>01/09/2024 au 01/12/2024</t>
-  </si>
-  <si>
-    <t>01/10/2025 au 01/04/2026</t>
-  </si>
-  <si>
-    <t>01/11/2024 au 01/12/2025</t>
-  </si>
-  <si>
-    <t>01/09/2025 au 01/09/2026</t>
-  </si>
-  <si>
-    <t>Veille Technologique</t>
-  </si>
-  <si>
-    <t>N° candidat : 02251774686</t>
   </si>
 </sst>
 </file>
@@ -322,7 +322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -402,6 +402,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -417,7 +428,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -436,51 +447,6 @@
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -552,7 +518,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -572,80 +538,71 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -955,134 +912,134 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ80"/>
+  <dimension ref="A1:AQ76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="182.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="104.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="103.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
     <col min="3" max="8" width="18.73046875" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.3984375" customWidth="1"/>
     <col min="44" max="16384" width="10.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="20"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="A3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="A5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="28" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I7"/>
@@ -1122,16 +1079,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1168,27 +1125,27 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="18" t="s">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="16"/>
+      <c r="B9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="24"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1226,22 +1183,22 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1279,26 +1236,26 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="16"/>
+      <c r="A11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="24"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1335,25 +1292,25 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="16"/>
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="24"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1391,18 +1348,18 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16" t="s">
+      <c r="A13" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I13"/>
@@ -1442,18 +1399,18 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16" t="s">
+      <c r="A14" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24" t="s">
         <v>23</v>
       </c>
       <c r="I14"/>
@@ -1493,14 +1450,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1537,15 +1494,17 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1582,15 +1541,23 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="61.15" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="24"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1627,15 +1594,23 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="61.15" x14ac:dyDescent="0.35">
+      <c r="A18" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="24"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1672,17 +1647,27 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="40.9" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="24"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1719,23 +1704,21 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="16"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="61.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1772,23 +1755,27 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="16"/>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="22.15" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="25"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1826,26 +1813,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="16"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1882,21 +1857,17 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1933,27 +1904,23 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="77.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="31"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -1990,15 +1957,23 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="24"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2035,17 +2010,25 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="50.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="24"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2082,23 +2065,21 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="16"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2135,23 +2116,23 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="16"/>
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="22.15" x14ac:dyDescent="0.35">
+      <c r="A28" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24" t="s">
+        <v>23</v>
+      </c>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2189,24 +2170,14 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="16"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2243,21 +2214,15 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2294,208 +2259,24 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31"/>
-      <c r="S31"/>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="W31"/>
-      <c r="X31"/>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31"/>
-      <c r="AB31"/>
-      <c r="AC31"/>
-      <c r="AD31"/>
-      <c r="AE31"/>
-      <c r="AF31"/>
-      <c r="AG31"/>
-      <c r="AH31"/>
-      <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31"/>
-      <c r="AL31"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
-    </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="7"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-      <c r="S32"/>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32"/>
-      <c r="W32"/>
-      <c r="X32"/>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32"/>
-      <c r="AB32"/>
-      <c r="AC32"/>
-      <c r="AD32"/>
-      <c r="AE32"/>
-      <c r="AF32"/>
-      <c r="AG32"/>
-      <c r="AH32"/>
-      <c r="AI32"/>
-      <c r="AJ32"/>
-      <c r="AK32"/>
-      <c r="AL32"/>
-      <c r="AM32"/>
-      <c r="AN32"/>
-      <c r="AO32"/>
-      <c r="AP32"/>
-      <c r="AQ32"/>
-    </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33"/>
-      <c r="AL33"/>
-      <c r="AM33"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-    </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34"/>
-      <c r="AL34"/>
-      <c r="AM34"/>
-      <c r="AN34"/>
-      <c r="AO34"/>
-      <c r="AP34"/>
-      <c r="AQ34"/>
-    </row>
-    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:43" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
@@ -2524,55 +2305,30 @@
     <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="42" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008922F4C6891A514CA757364D2E9E89FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a0f42147af918e631750b60230c82928">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad37bc74-7894-4de5-9998-ea92f4517356" xmlns:ns3="459bd866-d0f9-4759-8bda-70b032d02ba4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="224e6db4d0ca6805ab4b5b87e6abd390" ns2:_="" ns3:_="">
     <xsd:import namespace="ad37bc74-7894-4de5-9998-ea92f4517356"/>
@@ -2773,32 +2529,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Heure xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">2025-02-10T11:34:03+00:00</Date_x002f_Heure>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad37bc74-7894-4de5-9998-ea92f4517356">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="459bd866-d0f9-4759-8bda-70b032d02ba4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C96276-777E-40D0-A799-14F345054A77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2815,4 +2567,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE94479-FF3B-432A-9D24-4B1E26F2508C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA3C861-4EF5-4554-A18B-3B1408C768F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ad37bc74-7894-4de5-9998-ea92f4517356"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="459bd866-d0f9-4759-8bda-70b032d02ba4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>